--- a/corr_matrix/residual_exam4B_1PL.xlsx
+++ b/corr_matrix/residual_exam4B_1PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>4B02</t>
@@ -560,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0421945285913201</v>
+        <v>-0.04216828525120984</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2721105678563273</v>
+        <v>-0.2721150820272136</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.07441812213589376</v>
+        <v>-0.07442126795455803</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04178191521753574</v>
+        <v>0.04181307751618303</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.06762831942763257</v>
+        <v>-0.06763288779801056</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.19155168396763</v>
+        <v>-0.1915569732354255</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1240157081834263</v>
+        <v>-0.124023630678799</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.167300122933988</v>
+        <v>-0.1673061592162519</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.06244263687587841</v>
+        <v>-0.06242316304346181</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1390718435997557</v>
+        <v>-0.1390174862411304</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09116801150739166</v>
+        <v>0.09115849686285867</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1194208503971989</v>
+        <v>-0.1194078117776548</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1381810174866275</v>
+        <v>-0.1381779447815837</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.09865814175006875</v>
+        <v>-0.09864270906531647</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1195496640569203</v>
+        <v>0.1195928771223743</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.01693091130420991</v>
+        <v>-0.01688642847246664</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02266837508753234</v>
+        <v>-0.02267162620295323</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.02697390065605983</v>
+        <v>-0.0269684088201806</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.07152446709166359</v>
+        <v>-0.07152592416728147</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.2012685746848634</v>
+        <v>-0.2012666195229633</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.07999598317769721</v>
+        <v>-0.08004759832260569</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01051248021054335</v>
+        <v>0.01049874868447648</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1366466603820463</v>
+        <v>0.136685229335736</v>
       </c>
     </row>
     <row r="3">
@@ -636,76 +641,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0421945285913201</v>
+        <v>-0.04216828525120984</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1860488383765742</v>
+        <v>0.1860519914393787</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01166886966184991</v>
+        <v>-0.01168641226615496</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2578115958893131</v>
+        <v>-0.2578018622271122</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04662322965449267</v>
+        <v>0.04661607041639452</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1692412658713597</v>
+        <v>0.1692262927975758</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01950971574441845</v>
+        <v>0.0194974864314986</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.09260293651112869</v>
+        <v>-0.09262873077180424</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.02069484638543029</v>
+        <v>-0.0206533651483754</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1862332557256531</v>
+        <v>-0.1861594632742161</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1166535737238961</v>
+        <v>0.1166489586489325</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07476886959713029</v>
+        <v>0.07480537664794204</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1200551567834695</v>
+        <v>-0.1200430219093579</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.03689672777653912</v>
+        <v>-0.03685344061319311</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1155229248204404</v>
+        <v>-0.1154808682790709</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.121189503389916</v>
+        <v>-0.1211027380671363</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.09810426398599784</v>
+        <v>-0.0981050316113849</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2163924720457737</v>
+        <v>-0.2163929053709182</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2304637845733779</v>
+        <v>-0.2304564204404309</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2057043823613588</v>
+        <v>-0.2056846225123039</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.07736315235735061</v>
+        <v>-0.07742779248887799</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1606392403454677</v>
+        <v>-0.1606159177435941</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04060044732020938</v>
+        <v>0.04063017378628878</v>
       </c>
     </row>
     <row r="4">
@@ -715,76 +720,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2721105678563273</v>
+        <v>-0.2721150820272136</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1860488383765742</v>
+        <v>0.1860519914393787</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.09175594211090787</v>
+        <v>-0.09181154640803019</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01931119053479933</v>
+        <v>0.01925141643422635</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1042467833861418</v>
+        <v>0.1042036346451372</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.03819987464580005</v>
+        <v>-0.03818713357494879</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1081731898995324</v>
+        <v>0.1081854446183706</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.07093228847546369</v>
+        <v>-0.07095851705070164</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1101259108967289</v>
+        <v>0.1100751601348259</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1400619206115715</v>
+        <v>0.1400363703554296</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.22237189518535</v>
+        <v>-0.2223962142927924</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01575783578948426</v>
+        <v>-0.01577682668753235</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2313015707292318</v>
+        <v>-0.2313484358732837</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.01045628955249991</v>
+        <v>-0.01049573939283108</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2250228629514663</v>
+        <v>-0.2250226759286139</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1725552689918979</v>
+        <v>-0.1725501178319331</v>
       </c>
       <c r="S4" t="n">
-        <v>5.291045501794419e-05</v>
+        <v>7.619256697117844e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>0.125046092317452</v>
+        <v>0.1249727726425824</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1596638680579279</v>
+        <v>0.1596235744655116</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.09160045814776359</v>
+        <v>-0.09165893112125682</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.02886305136904941</v>
+        <v>-0.02894141646253096</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2253168069046109</v>
+        <v>-0.2253376495795069</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.02868701917064413</v>
+        <v>-0.02867277200958687</v>
       </c>
     </row>
     <row r="5">
@@ -794,76 +799,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.07441812213589376</v>
+        <v>-0.07442126795455803</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.01166886966184991</v>
+        <v>-0.01168641226615496</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.09175594211090787</v>
+        <v>-0.09181154640803019</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05628288320105087</v>
+        <v>0.05623509618365459</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.02928091884169078</v>
+        <v>-0.02932788226681425</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09635027868466056</v>
+        <v>0.09635221512792197</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04593689342103748</v>
+        <v>0.04594474372936445</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.111654564383373</v>
+        <v>-0.1116586318565528</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.174963061861585</v>
+        <v>-0.1750104021285464</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006837648262608049</v>
+        <v>0.006803256902278144</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2663564549908063</v>
+        <v>0.2663268843043992</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2140914464106433</v>
+        <v>-0.2141121619654532</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006946736799911781</v>
+        <v>0.006898617922090934</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.145721214152369</v>
+        <v>-0.1457616512245395</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06850443825277587</v>
+        <v>0.06849469491718686</v>
       </c>
       <c r="R5" t="n">
-        <v>0.09193355846288188</v>
+        <v>0.09189969621627452</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1303766900063141</v>
+        <v>0.130386077677877</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1306944915877327</v>
+        <v>0.1306513475236566</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1556208914057554</v>
+        <v>-0.1556588805976669</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09798022480373572</v>
+        <v>0.09794099325191898</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.152295976319861</v>
+        <v>-0.1523301001517721</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09543972678128136</v>
+        <v>0.09541410381351741</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.3926321858193307</v>
+        <v>-0.3926342714858874</v>
       </c>
     </row>
     <row r="6">
@@ -873,76 +878,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04178191521753574</v>
+        <v>0.04181307751618303</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2578115958893131</v>
+        <v>-0.2578018622271122</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01931119053479933</v>
+        <v>0.01925141643422635</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05628288320105087</v>
+        <v>0.05623509618365459</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1388758773176169</v>
+        <v>-0.1389302907770594</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2604351411371261</v>
+        <v>-0.2604323104125965</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02510330566543227</v>
+        <v>-0.02506667094011624</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1757133348766236</v>
+        <v>-0.1757245157111181</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04960379740472513</v>
+        <v>0.04955346510430315</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01796850721468864</v>
+        <v>0.01794567191567962</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08070479364555221</v>
+        <v>-0.08073447188681372</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1219059697941647</v>
+        <v>-0.121930385103752</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.09100248057358731</v>
+        <v>-0.0910510735663641</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.08853119103905355</v>
+        <v>-0.0885754971446175</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1408954231726909</v>
+        <v>-0.1408753439680202</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1315277460560752</v>
+        <v>-0.1315361616640883</v>
       </c>
       <c r="S6" t="n">
-        <v>0.08086023238837893</v>
+        <v>0.08087841414417643</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4033908477219779</v>
+        <v>0.4033511735489758</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08772855967058722</v>
+        <v>0.08769033938564284</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1309729639439322</v>
+        <v>0.1309246408733276</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01814034924056106</v>
+        <v>0.01811472677268652</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.03859220878558729</v>
+        <v>-0.03861843680238165</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1401489918976886</v>
+        <v>0.1401644259032397</v>
       </c>
     </row>
     <row r="7">
@@ -952,76 +957,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.06762831942763257</v>
+        <v>-0.06763288779801056</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04662322965449267</v>
+        <v>0.04661607041639452</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1042467833861418</v>
+        <v>0.1042036346451372</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02928091884169078</v>
+        <v>-0.02932788226681425</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1388758773176169</v>
+        <v>-0.1389302907770594</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0004280540359420499</v>
+        <v>0.0004403425955460169</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09592299782577138</v>
+        <v>0.09592857414397504</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.005248995575906163</v>
+        <v>-0.005262123426755564</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2361512825777007</v>
+        <v>-0.2362000986873507</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.123574880747859</v>
+        <v>-0.1236010337184362</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2036694225902453</v>
+        <v>0.2036639313592312</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3289756366429456</v>
+        <v>0.3289678203147479</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1622634148261734</v>
+        <v>-0.1622933734418373</v>
       </c>
       <c r="P7" t="n">
-        <v>0.07252132122063101</v>
+        <v>0.07249243400424364</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.001172172286859474</v>
+        <v>-0.001178117010421725</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.00615285965778819</v>
+        <v>-0.006155899697011115</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2231958250000327</v>
+        <v>-0.2231745895959966</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02664095781340823</v>
+        <v>0.0265813276673991</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2153396966101117</v>
+        <v>-0.2153803006279136</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3315009611529303</v>
+        <v>-0.3315485844230044</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1065064108131613</v>
+        <v>0.1064703423359962</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2857243035613902</v>
+        <v>-0.2857320639973723</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.04300265443997068</v>
+        <v>-0.04299242628093508</v>
       </c>
     </row>
     <row r="8">
@@ -1031,76 +1036,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.19155168396763</v>
+        <v>-0.1915569732354255</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1692412658713597</v>
+        <v>0.1692262927975758</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03819987464580005</v>
+        <v>-0.03818713357494879</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09635027868466056</v>
+        <v>0.09635221512792197</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2604351411371261</v>
+        <v>-0.2604323104125965</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004280540359420499</v>
+        <v>0.0004403425955460169</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1004447783788961</v>
+        <v>-0.1004539970781647</v>
       </c>
       <c r="J8" t="n">
-        <v>0.459769087285797</v>
+        <v>0.4597937719469891</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0990259081378952</v>
+        <v>0.09903536811733765</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0962967014591819</v>
+        <v>-0.09630129835224423</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1992981031319546</v>
+        <v>-0.1992807513777378</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02083562026796492</v>
+        <v>0.02085424764171831</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2799786359236333</v>
+        <v>0.2799843334772447</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1055853135257233</v>
+        <v>0.1055892050713494</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.08716121314875613</v>
+        <v>-0.08717855421915857</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.02734851659013648</v>
+        <v>-0.02735663649238263</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.02715623000279824</v>
+        <v>-0.02713238981277773</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.075172839209528</v>
+        <v>-0.07516058238066105</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.07511608518408538</v>
+        <v>-0.07509663447088863</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.06197731897122811</v>
+        <v>-0.06196538908660591</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.02468957052285113</v>
+        <v>-0.02465398803370295</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2213275882027306</v>
+        <v>-0.2213092688419234</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.1475513379993219</v>
+        <v>-0.1475635988523542</v>
       </c>
     </row>
     <row r="9">
@@ -1110,76 +1115,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1240157081834263</v>
+        <v>-0.124023630678799</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01950971574441845</v>
+        <v>0.0194974864314986</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1081731898995324</v>
+        <v>0.1081854446183706</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04593689342103748</v>
+        <v>0.04594474372936445</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.02510330566543227</v>
+        <v>-0.02506667094011624</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09592299782577138</v>
+        <v>0.09592857414397504</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1004447783788961</v>
+        <v>-0.1004539970781647</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2399984490982565</v>
+        <v>-0.2399968305492495</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3160064607511238</v>
+        <v>-0.3160040859945449</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.01637898806274592</v>
+        <v>-0.01635366905933323</v>
       </c>
       <c r="M9" t="n">
-        <v>0.007314103527137678</v>
+        <v>0.007310719720763414</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.02625212460504664</v>
+        <v>-0.02625323195158075</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2459856807466104</v>
+        <v>-0.245988274023217</v>
       </c>
       <c r="P9" t="n">
-        <v>0.07367508915194011</v>
+        <v>0.07367623846441344</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1279990530059698</v>
+        <v>-0.1279549350224215</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.02431161646202203</v>
+        <v>-0.02429904214821391</v>
       </c>
       <c r="S9" t="n">
-        <v>0.08035103747596616</v>
+        <v>0.08034560300641304</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.004794791824977335</v>
+        <v>-0.004782255913439968</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1135851978536551</v>
+        <v>-0.1135847286915244</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.03855295915175699</v>
+        <v>-0.03855091453672901</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.07500372550841018</v>
+        <v>-0.07503996477260307</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0348201890446139</v>
+        <v>0.03480202245498228</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.2102252547891903</v>
+        <v>-0.2101735534801003</v>
       </c>
     </row>
     <row r="10">
@@ -1189,76 +1194,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.167300122933988</v>
+        <v>-0.1673061592162519</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.09260293651112869</v>
+        <v>-0.09262873077180424</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.07093228847546369</v>
+        <v>-0.07095851705070164</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.111654564383373</v>
+        <v>-0.1116586318565528</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1757133348766236</v>
+        <v>-0.1757245157111181</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.005248995575906163</v>
+        <v>-0.005262123426755564</v>
       </c>
       <c r="H10" t="n">
-        <v>0.459769087285797</v>
+        <v>0.4597937719469891</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2399984490982565</v>
+        <v>-0.2399968305492495</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1368249529863938</v>
+        <v>0.1367734537361515</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3202725466277111</v>
+        <v>-0.3203069303731912</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3746540816898275</v>
+        <v>-0.3746493549974105</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1031869938965494</v>
+        <v>0.1031596085156589</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4677756798080704</v>
+        <v>0.4677581171319807</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1429441377365187</v>
+        <v>0.1428928447204125</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.07069298763066981</v>
+        <v>0.07067903698691649</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.2176795000782716</v>
+        <v>-0.2177043095210501</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1072501438677849</v>
+        <v>-0.107203062866475</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1332676061372246</v>
+        <v>-0.1333081219873899</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1873442953424262</v>
+        <v>0.1873111341838541</v>
       </c>
       <c r="V10" t="n">
-        <v>0.04975526775633721</v>
+        <v>0.04971677815828413</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1319065554809566</v>
+        <v>0.1318802786500211</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03583006486918625</v>
+        <v>0.035797110737226</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.103586575033488</v>
+        <v>-0.1035806482422826</v>
       </c>
     </row>
     <row r="11">
@@ -1268,76 +1273,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.06244263687587841</v>
+        <v>-0.06242316304346181</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.02069484638543029</v>
+        <v>-0.0206533651483754</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1101259108967289</v>
+        <v>0.1100751601348259</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.174963061861585</v>
+        <v>-0.1750104021285464</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04960379740472513</v>
+        <v>0.04955346510430315</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2361512825777007</v>
+        <v>-0.2362000986873507</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0990259081378952</v>
+        <v>0.09903536811733765</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3160064607511238</v>
+        <v>-0.3160040859945449</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1368249529863938</v>
+        <v>0.1367734537361515</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02022508618154153</v>
+        <v>0.02024759166504686</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3165002045666759</v>
+        <v>-0.3165151265118131</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2049479222267044</v>
+        <v>-0.20494043567131</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1108527110790073</v>
+        <v>0.1108385862518584</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.03208481707531376</v>
+        <v>-0.03208845324809203</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.0118517450817995</v>
+        <v>-0.01183536849231994</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.1647397740563488</v>
+        <v>-0.1646767020433917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.06244263814606661</v>
+        <v>-0.06242962668487563</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1639923731947499</v>
+        <v>0.1639320919680976</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09491274303197172</v>
+        <v>0.09487190327246187</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1946151141937859</v>
+        <v>0.1945879456102365</v>
       </c>
       <c r="W11" t="n">
-        <v>0.006552377612847517</v>
+        <v>0.006450750729959665</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1848362809028445</v>
+        <v>-0.1848299089594461</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.04519658210150417</v>
+        <v>-0.04517533072293516</v>
       </c>
     </row>
     <row r="12">
@@ -1347,76 +1352,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1390718435997557</v>
+        <v>-0.1390174862411304</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1862332557256531</v>
+        <v>-0.1861594632742161</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1400619206115715</v>
+        <v>0.1400363703554296</v>
       </c>
       <c r="E12" t="n">
-        <v>0.006837648262608049</v>
+        <v>0.006803256902278144</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01796850721468864</v>
+        <v>0.01794567191567962</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.123574880747859</v>
+        <v>-0.1236010337184362</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0962967014591819</v>
+        <v>-0.09630129835224423</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.01637898806274592</v>
+        <v>-0.01635366905933323</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3202725466277111</v>
+        <v>-0.3203069303731912</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02022508618154153</v>
+        <v>0.02024759166504686</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1101684843787072</v>
+        <v>-0.1101769410517168</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1060659301106762</v>
+        <v>-0.1060273483860814</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1756602288554193</v>
+        <v>-0.1756603109275906</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.05860353731904106</v>
+        <v>-0.05856697324632983</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1424940437948208</v>
+        <v>-0.1424330625098145</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.07752134351978017</v>
+        <v>-0.07742979475784108</v>
       </c>
       <c r="S12" t="n">
-        <v>0.07199781993020168</v>
+        <v>0.07198955149460436</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.04611816050495399</v>
+        <v>-0.04614612541150487</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.03562844424145738</v>
+        <v>-0.03564032142226927</v>
       </c>
       <c r="V12" t="n">
-        <v>0.06650917369886299</v>
+        <v>0.06650826590162465</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.140668270849629</v>
+        <v>-0.1407550396506816</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0452377947728121</v>
+        <v>0.04525527294756295</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.09192165170910513</v>
+        <v>0.09195269492136576</v>
       </c>
     </row>
     <row r="13">
@@ -1426,76 +1431,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09116801150739166</v>
+        <v>0.09115849686285867</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1166535737238961</v>
+        <v>0.1166489586489325</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.22237189518535</v>
+        <v>-0.2223962142927924</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2663564549908063</v>
+        <v>0.2663268843043992</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.08070479364555221</v>
+        <v>-0.08073447188681372</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2036694225902453</v>
+        <v>0.2036639313592312</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1992981031319546</v>
+        <v>-0.1992807513777378</v>
       </c>
       <c r="I13" t="n">
-        <v>0.007314103527137678</v>
+        <v>0.007310719720763414</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3746540816898275</v>
+        <v>-0.3746493549974105</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3165002045666759</v>
+        <v>-0.3165151265118131</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1101684843787072</v>
+        <v>-0.1101769410517168</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.07635475087420565</v>
+        <v>0.07637022463465667</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2703768963193998</v>
+        <v>-0.2703751249788307</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.03845382378730466</v>
+        <v>-0.03845589845576516</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.0764124443508907</v>
+        <v>-0.07641854546321071</v>
       </c>
       <c r="R13" t="n">
-        <v>0.192545146979188</v>
+        <v>0.1925475923154818</v>
       </c>
       <c r="S13" t="n">
-        <v>0.06754841975897735</v>
+        <v>0.06756882471126298</v>
       </c>
       <c r="T13" t="n">
-        <v>0.05788563045740409</v>
+        <v>0.05785808167822761</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1668860533509465</v>
+        <v>-0.1668922694466468</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2611830054817367</v>
+        <v>-0.2611901253932565</v>
       </c>
       <c r="W13" t="n">
-        <v>0.07717324948015021</v>
+        <v>0.07714533054406367</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1085606604061348</v>
+        <v>-0.1085391706931731</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.01722987279843275</v>
+        <v>-0.01722352840936077</v>
       </c>
     </row>
     <row r="14">
@@ -1505,76 +1510,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.1194208503971989</v>
+        <v>-0.1194078117776548</v>
       </c>
       <c r="C14" t="n">
-        <v>0.07476886959713029</v>
+        <v>0.07480537664794204</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.01575783578948426</v>
+        <v>-0.01577682668753235</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2140914464106433</v>
+        <v>-0.2141121619654532</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1219059697941647</v>
+        <v>-0.121930385103752</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3289756366429456</v>
+        <v>0.3289678203147479</v>
       </c>
       <c r="H14" t="n">
-        <v>0.02083562026796492</v>
+        <v>0.02085424764171831</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.02625212460504664</v>
+        <v>-0.02625323195158075</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1031869938965494</v>
+        <v>0.1031596085156589</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2049479222267044</v>
+        <v>-0.20494043567131</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1060659301106762</v>
+        <v>-0.1060273483860814</v>
       </c>
       <c r="M14" t="n">
-        <v>0.07635475087420565</v>
+        <v>0.07637022463465667</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.02001797848266985</v>
+        <v>-0.02000520425144024</v>
       </c>
       <c r="P14" t="n">
-        <v>0.002666164346476011</v>
+        <v>0.002690794675845556</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.006783517142679259</v>
+        <v>-0.006780427758798016</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.1995638782662285</v>
+        <v>-0.199484325835566</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.12600544318637</v>
+        <v>-0.125978878207196</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.09002744977169044</v>
+        <v>-0.09006101833212013</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01841274435140505</v>
+        <v>0.0184074125727993</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2253535216659122</v>
+        <v>-0.2253500831710154</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.05274930342794902</v>
+        <v>-0.05281393785097239</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1375337761900426</v>
+        <v>-0.1374937870080958</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.04152584467418529</v>
+        <v>-0.04151470622180772</v>
       </c>
     </row>
     <row r="15">
@@ -1584,76 +1589,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1381810174866275</v>
+        <v>-0.1381779447815837</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1200551567834695</v>
+        <v>-0.1200430219093579</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2313015707292318</v>
+        <v>-0.2313484358732837</v>
       </c>
       <c r="E15" t="n">
-        <v>0.006946736799911781</v>
+        <v>0.006898617922090934</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.09100248057358731</v>
+        <v>-0.0910510735663641</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1622634148261734</v>
+        <v>-0.1622933734418373</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2799786359236333</v>
+        <v>0.2799843334772447</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2459856807466104</v>
+        <v>-0.245988274023217</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4677756798080704</v>
+        <v>0.4677581171319807</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1108527110790073</v>
+        <v>0.1108385862518584</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1756602288554193</v>
+        <v>-0.1756603109275906</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2703768963193998</v>
+        <v>-0.2703751249788307</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.02001797848266985</v>
+        <v>-0.02000520425144024</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.006122817315133141</v>
+        <v>-0.006127714260766787</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1366390819827707</v>
+        <v>0.1366264343037622</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.06080657080910749</v>
+        <v>-0.06078523851726519</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.189267477945146</v>
+        <v>-0.1892513446928417</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1086711264468908</v>
+        <v>-0.1087241716159128</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1534014046592124</v>
+        <v>0.1533983743085265</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2080652186818404</v>
+        <v>0.2080533233104091</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01535389967987328</v>
+        <v>0.01533821595931927</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.08702181108093175</v>
+        <v>-0.08700660111435378</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.03008911114448147</v>
+        <v>-0.03008519178552964</v>
       </c>
     </row>
     <row r="16">
@@ -1663,76 +1668,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.09865814175006875</v>
+        <v>-0.09864270906531647</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.03689672777653912</v>
+        <v>-0.03685344061319311</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.01045628955249991</v>
+        <v>-0.01049573939283108</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.145721214152369</v>
+        <v>-0.1457616512245395</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.08853119103905355</v>
+        <v>-0.0885754971446175</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07252132122063101</v>
+        <v>0.07249243400424364</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1055853135257233</v>
+        <v>0.1055892050713494</v>
       </c>
       <c r="I16" t="n">
-        <v>0.07367508915194011</v>
+        <v>0.07367623846441344</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1429441377365187</v>
+        <v>0.1428928447204125</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.03208481707531376</v>
+        <v>-0.03208845324809203</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.05860353731904106</v>
+        <v>-0.05856697324632983</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.03845382378730466</v>
+        <v>-0.03845589845576516</v>
       </c>
       <c r="N16" t="n">
-        <v>0.002666164346476011</v>
+        <v>0.002690794675845556</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.006122817315133141</v>
+        <v>-0.006127714260766787</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1534331005896701</v>
+        <v>-0.153415386036642</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.1517237728846514</v>
+        <v>-0.1516469957335249</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2221506313525953</v>
+        <v>-0.2221366786279254</v>
       </c>
       <c r="T16" t="n">
-        <v>0.04188002904985523</v>
+        <v>0.04183145146313562</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1090849310359259</v>
+        <v>-0.1091103843854405</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1308971187615496</v>
+        <v>-0.1309104380383214</v>
       </c>
       <c r="W16" t="n">
-        <v>0.001971539553996937</v>
+        <v>0.001888429433978159</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.06921142000026603</v>
+        <v>-0.06918669185513508</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.1451889340483266</v>
+        <v>-0.1451676025989881</v>
       </c>
     </row>
     <row r="17">
@@ -1742,76 +1747,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1195496640569203</v>
+        <v>0.1195928771223743</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1155229248204404</v>
+        <v>-0.1154808682790709</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2250228629514663</v>
+        <v>-0.2250226759286139</v>
       </c>
       <c r="E17" t="n">
-        <v>0.06850443825277587</v>
+        <v>0.06849469491718686</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1408954231726909</v>
+        <v>-0.1408753439680202</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.001172172286859474</v>
+        <v>-0.001178117010421725</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.08716121314875613</v>
+        <v>-0.08717855421915857</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1279990530059698</v>
+        <v>-0.1279549350224215</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07069298763066981</v>
+        <v>0.07067903698691649</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0118517450817995</v>
+        <v>-0.01183536849231994</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1424940437948208</v>
+        <v>-0.1424330625098145</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0764124443508907</v>
+        <v>-0.07641854546321071</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.006783517142679259</v>
+        <v>-0.006780427758798016</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1366390819827707</v>
+        <v>0.1366264343037622</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1534331005896701</v>
+        <v>-0.153415386036642</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.08510044640348409</v>
+        <v>-0.08506406319261561</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.07342936557788479</v>
+        <v>-0.07344473024236846</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.08794364498070754</v>
+        <v>-0.08793955791744217</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1690994409270717</v>
+        <v>-0.1690858660628783</v>
       </c>
       <c r="V17" t="n">
-        <v>0.09157283676808373</v>
+        <v>0.09157375328971122</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.1114992024684923</v>
+        <v>-0.1114850891186221</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1062231188963337</v>
+        <v>-0.1062218245440063</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.005825763786877031</v>
+        <v>0.005882785495199979</v>
       </c>
     </row>
     <row r="18">
@@ -1821,76 +1826,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.01693091130420991</v>
+        <v>-0.01688642847246664</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.121189503389916</v>
+        <v>-0.1211027380671363</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1725552689918979</v>
+        <v>-0.1725501178319331</v>
       </c>
       <c r="E18" t="n">
-        <v>0.09193355846288188</v>
+        <v>0.09189969621627452</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1315277460560752</v>
+        <v>-0.1315361616640883</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.00615285965778819</v>
+        <v>-0.006155899697011115</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.02734851659013648</v>
+        <v>-0.02735663649238263</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.02431161646202203</v>
+        <v>-0.02429904214821391</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2176795000782716</v>
+        <v>-0.2177043095210501</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1647397740563488</v>
+        <v>-0.1646767020433917</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.07752134351978017</v>
+        <v>-0.07742979475784108</v>
       </c>
       <c r="M18" t="n">
-        <v>0.192545146979188</v>
+        <v>0.1925475923154818</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1995638782662285</v>
+        <v>-0.199484325835566</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.06080657080910749</v>
+        <v>-0.06078523851726519</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1517237728846514</v>
+        <v>-0.1516469957335249</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.08510044640348409</v>
+        <v>-0.08506406319261561</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.006754731890576363</v>
+        <v>-0.006761067900519805</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.128771742271269</v>
+        <v>-0.1287682418702404</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0711948330614862</v>
+        <v>-0.07116681469418</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.07320202217160077</v>
+        <v>-0.07316435532657943</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.2339575805686995</v>
+        <v>-0.2340016216346754</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3110735289514224</v>
+        <v>0.3111086978146835</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.1075873181930753</v>
+        <v>-0.1075635414036696</v>
       </c>
     </row>
     <row r="19">
@@ -1900,76 +1905,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02266837508753234</v>
+        <v>-0.02267162620295323</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.09810426398599784</v>
+        <v>-0.0981050316113849</v>
       </c>
       <c r="D19" t="n">
-        <v>5.291045501794419e-05</v>
+        <v>7.619256697117844e-05</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1303766900063141</v>
+        <v>0.130386077677877</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08086023238837893</v>
+        <v>0.08087841414417643</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2231958250000327</v>
+        <v>-0.2231745895959966</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.02715623000279824</v>
+        <v>-0.02713238981277773</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08035103747596616</v>
+        <v>0.08034560300641304</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1072501438677849</v>
+        <v>-0.107203062866475</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.06244263814606661</v>
+        <v>-0.06242962668487563</v>
       </c>
       <c r="L19" t="n">
-        <v>0.07199781993020168</v>
+        <v>0.07198955149460436</v>
       </c>
       <c r="M19" t="n">
-        <v>0.06754841975897735</v>
+        <v>0.06756882471126298</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.12600544318637</v>
+        <v>-0.125978878207196</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.189267477945146</v>
+        <v>-0.1892513446928417</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2221506313525953</v>
+        <v>-0.2221366786279254</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.07342936557788479</v>
+        <v>-0.07344473024236846</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.006754731890576363</v>
+        <v>-0.006761067900519805</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.03543425938531719</v>
+        <v>-0.03541098130640002</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.04240767195142028</v>
+        <v>-0.04238287839132996</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1814760976348879</v>
+        <v>0.181495238592897</v>
       </c>
       <c r="W19" t="n">
-        <v>0.007196774462806931</v>
+        <v>0.007239761081571467</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.01249156132298518</v>
+        <v>-0.01247531633588224</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.08151982563160452</v>
+        <v>0.08149871849897933</v>
       </c>
     </row>
     <row r="20">
@@ -1979,76 +1984,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.02697390065605983</v>
+        <v>-0.0269684088201806</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.2163924720457737</v>
+        <v>-0.2163929053709182</v>
       </c>
       <c r="D20" t="n">
-        <v>0.125046092317452</v>
+        <v>0.1249727726425824</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1306944915877327</v>
+        <v>0.1306513475236566</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4033908477219779</v>
+        <v>0.4033511735489758</v>
       </c>
       <c r="G20" t="n">
-        <v>0.02664095781340823</v>
+        <v>0.0265813276673991</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.075172839209528</v>
+        <v>-0.07516058238066105</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.004794791824977335</v>
+        <v>-0.004782255913439968</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1332676061372246</v>
+        <v>-0.1333081219873899</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1639923731947499</v>
+        <v>0.1639320919680976</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.04611816050495399</v>
+        <v>-0.04614612541150487</v>
       </c>
       <c r="M20" t="n">
-        <v>0.05788563045740409</v>
+        <v>0.05785808167822761</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.09002744977169044</v>
+        <v>-0.09006101833212013</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1086711264468908</v>
+        <v>-0.1087241716159128</v>
       </c>
       <c r="P20" t="n">
-        <v>0.04188002904985523</v>
+        <v>0.04183145146313562</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.08794364498070754</v>
+        <v>-0.08793955791744217</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.128771742271269</v>
+        <v>-0.1287682418702404</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.03543425938531719</v>
+        <v>-0.03541098130640002</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.08815701985077187</v>
+        <v>-0.08823281748888803</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.01659082097359968</v>
+        <v>-0.01666229811489259</v>
       </c>
       <c r="W20" t="n">
-        <v>0.001017892332708025</v>
+        <v>0.000921010493228439</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1685537425541325</v>
+        <v>-0.1685876192083765</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.1822324883353776</v>
+        <v>-0.1822178487348738</v>
       </c>
     </row>
     <row r="21">
@@ -2058,76 +2063,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.07152446709166359</v>
+        <v>-0.07152592416728147</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.2304637845733779</v>
+        <v>-0.2304564204404309</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1596638680579279</v>
+        <v>0.1596235744655116</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1556208914057554</v>
+        <v>-0.1556588805976669</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08772855967058722</v>
+        <v>0.08769033938564284</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2153396966101117</v>
+        <v>-0.2153803006279136</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.07511608518408538</v>
+        <v>-0.07509663447088863</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1135851978536551</v>
+        <v>-0.1135847286915244</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1873442953424262</v>
+        <v>0.1873111341838541</v>
       </c>
       <c r="K21" t="n">
-        <v>0.09491274303197172</v>
+        <v>0.09487190327246187</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.03562844424145738</v>
+        <v>-0.03564032142226927</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1668860533509465</v>
+        <v>-0.1668922694466468</v>
       </c>
       <c r="N21" t="n">
-        <v>0.01841274435140505</v>
+        <v>0.0184074125727993</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1534014046592124</v>
+        <v>0.1533983743085265</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1090849310359259</v>
+        <v>-0.1091103843854405</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1690994409270717</v>
+        <v>-0.1690858660628783</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.0711948330614862</v>
+        <v>-0.07116681469418</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.04240767195142028</v>
+        <v>-0.04238287839132996</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.08815701985077187</v>
+        <v>-0.08823281748888803</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1339321191496367</v>
+        <v>-0.1339758048750461</v>
       </c>
       <c r="W21" t="n">
-        <v>0.07654781827091231</v>
+        <v>0.07643198255593132</v>
       </c>
       <c r="X21" t="n">
-        <v>0.04892980763678168</v>
+        <v>0.04892342335561664</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.04813308758744232</v>
+        <v>0.04815813222763483</v>
       </c>
     </row>
     <row r="22">
@@ -2137,76 +2142,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.2012685746848634</v>
+        <v>-0.2012666195229633</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.2057043823613588</v>
+        <v>-0.2056846225123039</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.09160045814776359</v>
+        <v>-0.09165893112125682</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09798022480373572</v>
+        <v>0.09794099325191898</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1309729639439322</v>
+        <v>0.1309246408733276</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3315009611529303</v>
+        <v>-0.3315485844230044</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.06197731897122811</v>
+        <v>-0.06196538908660591</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.03855295915175699</v>
+        <v>-0.03855091453672901</v>
       </c>
       <c r="J22" t="n">
-        <v>0.04975526775633721</v>
+        <v>0.04971677815828413</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1946151141937859</v>
+        <v>0.1945879456102365</v>
       </c>
       <c r="L22" t="n">
-        <v>0.06650917369886299</v>
+        <v>0.06650826590162465</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2611830054817367</v>
+        <v>-0.2611901253932565</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2253535216659122</v>
+        <v>-0.2253500831710154</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2080652186818404</v>
+        <v>0.2080533233104091</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1308971187615496</v>
+        <v>-0.1309104380383214</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.09157283676808373</v>
+        <v>0.09157375328971122</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.07320202217160077</v>
+        <v>-0.07316435532657943</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1814760976348879</v>
+        <v>0.181495238592897</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.01659082097359968</v>
+        <v>-0.01666229811489259</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1339321191496367</v>
+        <v>-0.1339758048750461</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.01797374521821545</v>
+        <v>-0.01806423711189334</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1419806176892602</v>
+        <v>0.1419864935104466</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.1080504469008689</v>
+        <v>-0.108032956457206</v>
       </c>
     </row>
     <row r="23">
@@ -2216,76 +2221,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.07999598317769721</v>
+        <v>-0.08004759832260569</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.07736315235735061</v>
+        <v>-0.07742779248887799</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.02886305136904941</v>
+        <v>-0.02894141646253096</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.152295976319861</v>
+        <v>-0.1523301001517721</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01814034924056106</v>
+        <v>0.01811472677268652</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1065064108131613</v>
+        <v>0.1064703423359962</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.02468957052285113</v>
+        <v>-0.02465398803370295</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.07500372550841018</v>
+        <v>-0.07503996477260307</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1319065554809566</v>
+        <v>0.1318802786500211</v>
       </c>
       <c r="K23" t="n">
-        <v>0.006552377612847517</v>
+        <v>0.006450750729959665</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.140668270849629</v>
+        <v>-0.1407550396506816</v>
       </c>
       <c r="M23" t="n">
-        <v>0.07717324948015021</v>
+        <v>0.07714533054406367</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.05274930342794902</v>
+        <v>-0.05281393785097239</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01535389967987328</v>
+        <v>0.01533821595931927</v>
       </c>
       <c r="P23" t="n">
-        <v>0.001971539553996937</v>
+        <v>0.001888429433978159</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1114992024684923</v>
+        <v>-0.1114850891186221</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.2339575805686995</v>
+        <v>-0.2340016216346754</v>
       </c>
       <c r="S23" t="n">
-        <v>0.007196774462806931</v>
+        <v>0.007239761081571467</v>
       </c>
       <c r="T23" t="n">
-        <v>0.001017892332708025</v>
+        <v>0.000921010493228439</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07654781827091231</v>
+        <v>0.07643198255593132</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.01797374521821545</v>
+        <v>-0.01806423711189334</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1682085492073514</v>
+        <v>-0.1683135020680745</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.09789787758950418</v>
+        <v>0.09796940529998632</v>
       </c>
     </row>
     <row r="24">
@@ -2295,76 +2300,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.01051248021054335</v>
+        <v>0.01049874868447648</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1606392403454677</v>
+        <v>-0.1606159177435941</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2253168069046109</v>
+        <v>-0.2253376495795069</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09543972678128136</v>
+        <v>0.09541410381351741</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.03859220878558729</v>
+        <v>-0.03861843680238165</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2857243035613902</v>
+        <v>-0.2857320639973723</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2213275882027306</v>
+        <v>-0.2213092688419234</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0348201890446139</v>
+        <v>0.03480202245498228</v>
       </c>
       <c r="J24" t="n">
-        <v>0.03583006486918625</v>
+        <v>0.035797110737226</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1848362809028445</v>
+        <v>-0.1848299089594461</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0452377947728121</v>
+        <v>0.04525527294756295</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1085606604061348</v>
+        <v>-0.1085391706931731</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1375337761900426</v>
+        <v>-0.1374937870080958</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.08702181108093175</v>
+        <v>-0.08700660111435378</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.06921142000026603</v>
+        <v>-0.06918669185513508</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.1062231188963337</v>
+        <v>-0.1062218245440063</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3110735289514224</v>
+        <v>0.3111086978146835</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.01249156132298518</v>
+        <v>-0.01247531633588224</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1685537425541325</v>
+        <v>-0.1685876192083765</v>
       </c>
       <c r="U24" t="n">
-        <v>0.04892980763678168</v>
+        <v>0.04892342335561664</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1419806176892602</v>
+        <v>0.1419864935104466</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.1682085492073514</v>
+        <v>-0.1683135020680745</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.1669669839787161</v>
+        <v>-0.166946949042188</v>
       </c>
     </row>
     <row r="25">
@@ -2374,73 +2379,73 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1366466603820463</v>
+        <v>0.136685229335736</v>
       </c>
       <c r="C25" t="n">
-        <v>0.04060044732020938</v>
+        <v>0.04063017378628878</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.02868701917064413</v>
+        <v>-0.02867277200958687</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3926321858193307</v>
+        <v>-0.3926342714858874</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1401489918976886</v>
+        <v>0.1401644259032397</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.04300265443997068</v>
+        <v>-0.04299242628093508</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1475513379993219</v>
+        <v>-0.1475635988523542</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2102252547891903</v>
+        <v>-0.2101735534801003</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.103586575033488</v>
+        <v>-0.1035806482422826</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.04519658210150417</v>
+        <v>-0.04517533072293516</v>
       </c>
       <c r="L25" t="n">
-        <v>0.09192165170910513</v>
+        <v>0.09195269492136576</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.01722987279843275</v>
+        <v>-0.01722352840936077</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.04152584467418529</v>
+        <v>-0.04151470622180772</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.03008911114448147</v>
+        <v>-0.03008519178552964</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.1451889340483266</v>
+        <v>-0.1451676025989881</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.005825763786877031</v>
+        <v>0.005882785495199979</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.1075873181930753</v>
+        <v>-0.1075635414036696</v>
       </c>
       <c r="S25" t="n">
-        <v>0.08151982563160452</v>
+        <v>0.08149871849897933</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1822324883353776</v>
+        <v>-0.1822178487348738</v>
       </c>
       <c r="U25" t="n">
-        <v>0.04813308758744232</v>
+        <v>0.04815813222763483</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1080504469008689</v>
+        <v>-0.108032956457206</v>
       </c>
       <c r="W25" t="n">
-        <v>0.09789787758950418</v>
+        <v>0.09796940529998632</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1669669839787161</v>
+        <v>-0.166946949042188</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
